--- a/Docs/QA-Testing/RTM.xlsx
+++ b/Docs/QA-Testing/RTM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/admin/Downloads/Online-Store/Docs/QA-Testing/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\KiemChungPhanMem\Docs\QA-Testing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5C0424D-7F93-C14E-B174-17AC98FCE003}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05B68305-4436-49E8-B60E-BA12DB1D22E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="33600" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="123">
   <si>
     <t>Requirement ID</t>
   </si>
@@ -187,9 +187,6 @@
     <t>TC_FE_CUS_REG_01→06</t>
   </si>
   <si>
-    <t>PARTIAL PASS</t>
-  </si>
-  <si>
     <t>SCRUM-47</t>
   </si>
   <si>
@@ -214,9 +211,6 @@
     <t>API</t>
   </si>
   <si>
-    <t>FAIL</t>
-  </si>
-  <si>
     <t>TC-USER-07, TC-USER-10</t>
   </si>
   <si>
@@ -274,9 +268,6 @@
     <t>TC-PROD-05,10</t>
   </si>
   <si>
-    <t>SCRUM-43,44</t>
-  </si>
-  <si>
     <t>TC-PROD-06,09</t>
   </si>
   <si>
@@ -376,32 +367,35 @@
     <t>SCRUM-59</t>
   </si>
   <si>
-    <t>Tình trạng vá</t>
-  </si>
-  <si>
-    <t>PATCHED</t>
-  </si>
-  <si>
-    <t>Người thực hiện</t>
-  </si>
-  <si>
-    <t>THANH</t>
-  </si>
-  <si>
-    <t>THÙY</t>
-  </si>
-  <si>
-    <t>THÀNH</t>
-  </si>
-  <si>
-    <t>THANH, THÙY</t>
+    <t>PASS (Retest PASS; SCRUM-47 PATCHED)</t>
+  </si>
+  <si>
+    <t>PASS (SCRUM-45 PATCHED)</t>
+  </si>
+  <si>
+    <t>PASS (SCRUM-58 PATCHED)</t>
+  </si>
+  <si>
+    <t>PASS (46/49/50/51 PATCHED)</t>
+  </si>
+  <si>
+    <t>PASS (43/44/81 PATCHED)</t>
+  </si>
+  <si>
+    <t>SCRUM-43,44,81</t>
+  </si>
+  <si>
+    <t>PASS (48 PATCHED)</t>
+  </si>
+  <si>
+    <t>PASS (SCRUM-59 PATCHED)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -485,7 +479,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -507,6 +501,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -783,23 +780,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K23"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:I23"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.44140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="42" customWidth="1"/>
     <col min="3" max="3" width="20" customWidth="1"/>
     <col min="4" max="4" width="13" customWidth="1"/>
     <col min="5" max="5" width="18" customWidth="1"/>
     <col min="6" max="6" width="32" customWidth="1"/>
     <col min="7" max="7" width="42" customWidth="1"/>
-    <col min="8" max="8" width="23.5" customWidth="1"/>
-    <col min="9" max="9" width="13.1640625" customWidth="1"/>
-    <col min="10" max="10" width="16.6640625" customWidth="1"/>
-    <col min="11" max="11" width="17.6640625" customWidth="1"/>
+    <col min="8" max="8" width="23.44140625" customWidth="1"/>
+    <col min="9" max="9" width="13.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="36" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" ht="33.6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -827,14 +822,8 @@
       <c r="I1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="J1" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" ht="36" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:9" ht="50.4">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -857,19 +846,13 @@
         <v>54</v>
       </c>
       <c r="H2" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="I2" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="I2" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" ht="18" x14ac:dyDescent="0.2">
+    </row>
+    <row r="3" spans="1:9" ht="33.6">
       <c r="A3" s="2" t="s">
         <v>8</v>
       </c>
@@ -886,25 +869,19 @@
         <v>7</v>
       </c>
       <c r="F3" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="H3" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="H3" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" ht="18" x14ac:dyDescent="0.2">
+    </row>
+    <row r="4" spans="1:9" ht="33.6">
       <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
@@ -915,7 +892,7 @@
         <v>52</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>7</v>
@@ -928,43 +905,35 @@
         <v>46</v>
       </c>
       <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2"/>
-    </row>
-    <row r="5" spans="1:11" ht="18" x14ac:dyDescent="0.2">
+    </row>
+    <row r="5" spans="1:9" ht="33.6">
       <c r="A5" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>61</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>62</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>6</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="2" t="s">
-        <v>64</v>
+        <v>117</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" ht="18" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="33.6">
       <c r="A6" s="3" t="s">
         <v>14</v>
       </c>
@@ -975,25 +944,23 @@
         <v>16</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>7</v>
       </c>
       <c r="F6" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="H6" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="G6" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>67</v>
-      </c>
       <c r="I6" s="3"/>
-      <c r="J6" s="3"/>
-      <c r="K6" s="3"/>
-    </row>
-    <row r="7" spans="1:11" ht="18" x14ac:dyDescent="0.2">
+    </row>
+    <row r="7" spans="1:9" ht="33.6">
       <c r="A7" s="3" t="s">
         <v>17</v>
       </c>
@@ -1004,33 +971,31 @@
         <v>16</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>7</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="I7" s="3"/>
-      <c r="J7" s="3"/>
-      <c r="K7" s="3"/>
-    </row>
-    <row r="8" spans="1:11" ht="36" x14ac:dyDescent="0.2">
+    </row>
+    <row r="8" spans="1:9" ht="33.6">
       <c r="A8" s="2" t="s">
         <v>19</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>6</v>
@@ -1039,27 +1004,25 @@
         <v>7</v>
       </c>
       <c r="F8" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H8" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="G8" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>73</v>
-      </c>
       <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
-    </row>
-    <row r="9" spans="1:11" ht="18" x14ac:dyDescent="0.2">
+    </row>
+    <row r="9" spans="1:9" ht="33.6">
       <c r="A9" s="2" t="s">
         <v>20</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>6</v>
@@ -1068,56 +1031,52 @@
         <v>7</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>46</v>
       </c>
       <c r="I9" s="2"/>
-      <c r="J9" s="2"/>
-      <c r="K9" s="2"/>
-    </row>
-    <row r="10" spans="1:11" ht="18" x14ac:dyDescent="0.2">
+    </row>
+    <row r="10" spans="1:9" ht="33.6">
       <c r="A10" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="G10" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="H10" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
-    </row>
-    <row r="11" spans="1:11" ht="36" x14ac:dyDescent="0.2">
+    </row>
+    <row r="11" spans="1:9" ht="33.6">
       <c r="A11" s="2" t="s">
         <v>22</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>6</v>
@@ -1126,25 +1085,19 @@
         <v>23</v>
       </c>
       <c r="F11" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="I11" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="G11" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" ht="36" x14ac:dyDescent="0.2">
+    </row>
+    <row r="12" spans="1:9" ht="33.6">
       <c r="A12" s="2" t="s">
         <v>24</v>
       </c>
@@ -1152,7 +1105,7 @@
         <v>25</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>6</v>
@@ -1161,25 +1114,19 @@
         <v>7</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>26</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>55</v>
+        <v>119</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="K12" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" ht="18" x14ac:dyDescent="0.2">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="33.6">
       <c r="A13" s="2" t="s">
         <v>27</v>
       </c>
@@ -1187,33 +1134,31 @@
         <v>28</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E13" s="4" t="s">
         <v>23</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>46</v>
       </c>
       <c r="I13" s="2"/>
-      <c r="J13" s="2"/>
-      <c r="K13" s="2"/>
-    </row>
-    <row r="14" spans="1:11" ht="36" x14ac:dyDescent="0.2">
+    </row>
+    <row r="14" spans="1:9" ht="33.6">
       <c r="A14" s="3" t="s">
         <v>29</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>30</v>
@@ -1225,42 +1170,36 @@
         <v>7</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>55</v>
+        <v>121</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" ht="18" x14ac:dyDescent="0.2">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="33.6">
       <c r="A15" s="3" t="s">
         <v>31</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>30</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>7</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>32</v>
@@ -1269,27 +1208,25 @@
         <v>46</v>
       </c>
       <c r="I15" s="3"/>
-      <c r="J15" s="3"/>
-      <c r="K15" s="3"/>
-    </row>
-    <row r="16" spans="1:11" ht="18" x14ac:dyDescent="0.2">
+    </row>
+    <row r="16" spans="1:9" ht="33.6">
       <c r="A16" s="3" t="s">
         <v>33</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>30</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>7</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>34</v>
@@ -1298,27 +1235,25 @@
         <v>46</v>
       </c>
       <c r="I16" s="3"/>
-      <c r="J16" s="3"/>
-      <c r="K16" s="3"/>
-    </row>
-    <row r="17" spans="1:11" ht="18" x14ac:dyDescent="0.2">
+    </row>
+    <row r="17" spans="1:9" ht="33.6">
       <c r="A17" s="3" t="s">
         <v>35</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>30</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>36</v>
@@ -1327,15 +1262,13 @@
         <v>46</v>
       </c>
       <c r="I17" s="3"/>
-      <c r="J17" s="3"/>
-      <c r="K17" s="3"/>
-    </row>
-    <row r="18" spans="1:11" ht="18" x14ac:dyDescent="0.2">
+    </row>
+    <row r="18" spans="1:9" ht="33.6">
       <c r="A18" s="3" t="s">
         <v>37</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>30</v>
@@ -1347,24 +1280,22 @@
         <v>7</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>46</v>
       </c>
       <c r="I18" s="3"/>
-      <c r="J18" s="3"/>
-      <c r="K18" s="3"/>
-    </row>
-    <row r="19" spans="1:11" ht="36" x14ac:dyDescent="0.2">
+    </row>
+    <row r="19" spans="1:9" ht="33.6">
       <c r="A19" s="2" t="s">
         <v>38</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>39</v>
@@ -1376,7 +1307,7 @@
         <v>7</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>40</v>
@@ -1385,21 +1316,15 @@
         <v>46</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="K19" s="2" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" ht="18" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="16.8">
       <c r="A20" s="2" t="s">
         <v>41</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>39</v>
@@ -1411,19 +1336,17 @@
         <v>7</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>46</v>
       </c>
       <c r="I20" s="2"/>
-      <c r="J20" s="2"/>
-      <c r="K20" s="2"/>
-    </row>
-    <row r="21" spans="1:11" ht="18" x14ac:dyDescent="0.2">
+    </row>
+    <row r="21" spans="1:9" ht="16.8">
       <c r="A21" s="2" t="s">
         <v>42</v>
       </c>
@@ -1440,7 +1363,7 @@
         <v>7</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>44</v>
@@ -1449,15 +1372,13 @@
         <v>46</v>
       </c>
       <c r="I21" s="2"/>
-      <c r="J21" s="2"/>
-      <c r="K21" s="2"/>
-    </row>
-    <row r="22" spans="1:11" ht="36" x14ac:dyDescent="0.2">
+    </row>
+    <row r="22" spans="1:9" ht="33.6">
       <c r="A22" s="2" t="s">
         <v>45</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>39</v>
@@ -1469,24 +1390,22 @@
         <v>7</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>46</v>
       </c>
       <c r="I22" s="2"/>
-      <c r="J22" s="2"/>
-      <c r="K22" s="2"/>
-    </row>
-    <row r="23" spans="1:11" ht="18" x14ac:dyDescent="0.2">
+    </row>
+    <row r="23" spans="1:9" ht="33.6">
       <c r="A23" s="2" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>39</v>
@@ -1495,25 +1414,19 @@
         <v>6</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="H23" s="6" t="s">
-        <v>64</v>
+        <v>113</v>
+      </c>
+      <c r="H23" s="8" t="s">
+        <v>122</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="J23" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="K23" s="5" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
     </row>
   </sheetData>

--- a/Docs/QA-Testing/RTM.xlsx
+++ b/Docs/QA-Testing/RTM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\KiemChungPhanMem\Docs\QA-Testing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05B68305-4436-49E8-B60E-BA12DB1D22E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59882DFE-B354-4199-9B89-EDF2EB5C384E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
